--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69631356-CCEE-4672-99A3-35CFF681E214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01167284-13ED-4128-8A27-F28FDD157D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15400" yWindow="2990" windowWidth="21100" windowHeight="15810" xr2:uid="{2060C4C8-3805-4E23-AE6B-F728D7027876}"/>
+    <workbookView xWindow="9060" yWindow="130" windowWidth="29080" windowHeight="15460" activeTab="1" xr2:uid="{2060C4C8-3805-4E23-AE6B-F728D7027876}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -2611,15 +2611,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>24430</xdr:colOff>
+      <xdr:colOff>63083</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>33131</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>24430</xdr:colOff>
+      <xdr:colOff>63083</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>107156</xdr:rowOff>
+      <xdr:rowOff>140287</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2634,7 +2634,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16550995" y="0"/>
+          <a:off x="16589648" y="33131"/>
           <a:ext cx="0" cy="16064982"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>40</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>181240</v>
+        <v>219753.5</v>
       </c>
       <c r="M4" s="3"/>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="L7" s="2">
         <f>+L4-L5+L6</f>
-        <v>188191</v>
+        <v>226704.5</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
@@ -5584,11 +5584,24 @@
       <c r="Q19" s="5">
         <v>4732</v>
       </c>
+      <c r="S19" s="5">
+        <v>4356</v>
+      </c>
       <c r="T19" s="5">
-        <v>4320</v>
+        <v>4282</v>
       </c>
       <c r="U19" s="5">
-        <v>4352</v>
+        <v>4339</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5">
+        <v>4667</v>
+      </c>
+      <c r="X19" s="5">
+        <v>4417</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>4235</v>
       </c>
       <c r="CH19" s="2">
         <v>700</v>
@@ -5625,6 +5638,7 @@
       <c r="U20" s="3">
         <v>412</v>
       </c>
+      <c r="Y20" s="5"/>
       <c r="CH20" s="2">
         <v>700</v>
       </c>
@@ -5660,6 +5674,7 @@
       <c r="U21" s="5">
         <v>485</v>
       </c>
+      <c r="Y21" s="5"/>
       <c r="CH21" s="2">
         <v>1000</v>
       </c>
@@ -5695,6 +5710,7 @@
       <c r="U22" s="5">
         <v>1511</v>
       </c>
+      <c r="Y22" s="5"/>
       <c r="CH22" s="2">
         <v>7100</v>
       </c>
@@ -5725,13 +5741,22 @@
         <v>3076</v>
       </c>
       <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
+      <c r="S23" s="5">
+        <v>3828</v>
+      </c>
       <c r="T23" s="5">
-        <v>3045</v>
+        <v>3805</v>
       </c>
       <c r="U23" s="5">
         <v>3349</v>
       </c>
+      <c r="W23" s="5">
+        <v>4126</v>
+      </c>
+      <c r="X23" s="5">
+        <v>3939</v>
+      </c>
+      <c r="Y23" s="5"/>
       <c r="CH23" s="2">
         <v>23400</v>
       </c>
@@ -5767,6 +5792,7 @@
       <c r="U24" s="3">
         <v>372</v>
       </c>
+      <c r="Y24" s="5"/>
       <c r="CH24" s="2">
         <v>4500</v>
       </c>
@@ -5900,7 +5926,9 @@
         <v>4503</v>
       </c>
       <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
+      <c r="S26" s="5">
+        <v>8273</v>
+      </c>
       <c r="T26" s="5">
         <v>4480</v>
       </c>
@@ -5908,8 +5936,12 @@
         <v>4888</v>
       </c>
       <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
+      <c r="W26" s="5">
+        <v>7629</v>
+      </c>
+      <c r="X26" s="5">
+        <v>7871</v>
+      </c>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
@@ -6950,7 +6982,7 @@
         <v>16420</v>
       </c>
       <c r="CM30" s="2">
-        <f t="shared" ref="CM30:CW30" si="55">+CL30*1.03</f>
+        <f t="shared" ref="CM30" si="55">+CL30*1.03</f>
         <v>16912.600000000002</v>
       </c>
       <c r="CN30" s="2">
@@ -7169,7 +7201,7 @@
         <v>5268</v>
       </c>
       <c r="CM31" s="2">
-        <f t="shared" ref="CM31:CW31" si="57">+CL31*1.03</f>
+        <f t="shared" ref="CM31" si="57">+CL31*1.03</f>
         <v>5426.04</v>
       </c>
       <c r="CN31" s="2">
@@ -10417,7 +10449,7 @@
       <c r="CW45" s="4"/>
       <c r="DA45" s="4">
         <f>+DA44/Main!L2-1</f>
-        <v>-0.25534376156805005</v>
+        <v>-0.38585052500457728</v>
       </c>
     </row>
     <row r="47" spans="2:179" x14ac:dyDescent="0.25">
@@ -11291,31 +11323,31 @@
       </c>
       <c r="R64" s="5"/>
       <c r="S64" s="5">
-        <f>SUM(S57:S63)</f>
+        <f t="shared" ref="S64:Y64" si="225">SUM(S57:S63)</f>
         <v>192733</v>
       </c>
       <c r="T64" s="5">
-        <f>SUM(T57:T63)</f>
+        <f t="shared" si="225"/>
         <v>206205</v>
       </c>
       <c r="U64" s="5">
-        <f>SUM(U57:U63)</f>
+        <f t="shared" si="225"/>
         <v>193542</v>
       </c>
       <c r="V64" s="5">
-        <f>SUM(V57:V63)</f>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="W64" s="5">
-        <f>SUM(W57:W63)</f>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="X64" s="5">
-        <f>SUM(X57:X63)</f>
+        <f t="shared" si="225"/>
         <v>192520</v>
       </c>
       <c r="Y64" s="5">
-        <f>SUM(Y57:Y63)</f>
+        <f t="shared" si="225"/>
         <v>204514</v>
       </c>
     </row>
@@ -11324,123 +11356,123 @@
         <v>37</v>
       </c>
       <c r="O66" s="5">
-        <f t="shared" ref="O66:R66" si="225">+O37</f>
+        <f t="shared" ref="O66:R66" si="226">+O37</f>
         <v>-1263</v>
       </c>
       <c r="P66" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>-592</v>
       </c>
       <c r="Q66" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>955</v>
       </c>
       <c r="R66" s="5">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>1432</v>
       </c>
       <c r="S66" s="5">
-        <f>+S37</f>
+        <f t="shared" ref="S66:Z66" si="227">+S37</f>
         <v>-576</v>
       </c>
       <c r="T66" s="5">
-        <f>+T37</f>
+        <f t="shared" si="227"/>
         <v>-941</v>
       </c>
       <c r="U66" s="5">
-        <f>+U37</f>
+        <f t="shared" si="227"/>
         <v>-3305</v>
       </c>
       <c r="V66" s="5">
-        <f>+V37</f>
+        <f t="shared" si="227"/>
         <v>796.15999999999985</v>
       </c>
       <c r="W66" s="5">
-        <f>+W37</f>
+        <f t="shared" si="227"/>
         <v>-619</v>
       </c>
       <c r="X66" s="5">
-        <f>+X37</f>
+        <f t="shared" si="227"/>
         <v>-1541</v>
       </c>
       <c r="Y66" s="5">
-        <f>+Y37</f>
+        <f t="shared" si="227"/>
         <v>554</v>
       </c>
       <c r="Z66" s="5">
-        <f>+Z37</f>
+        <f t="shared" si="227"/>
         <v>4991.5440000000008</v>
       </c>
       <c r="BS66" s="2">
-        <f t="shared" ref="BS66:BZ66" si="226">+BS37</f>
+        <f t="shared" ref="BS66:BZ66" si="228">+BS37</f>
         <v>7705</v>
       </c>
       <c r="BT66" s="28">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>3023</v>
       </c>
       <c r="BU66" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>5765</v>
       </c>
       <c r="BV66" s="28">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>6782</v>
       </c>
       <c r="BW66" s="28">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>4479</v>
       </c>
       <c r="BX66" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>10916</v>
       </c>
       <c r="BY66" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>12706</v>
       </c>
       <c r="BZ66" s="2">
-        <f t="shared" si="226"/>
+        <f t="shared" si="228"/>
         <v>10984</v>
       </c>
       <c r="CA66" s="2">
-        <f t="shared" ref="CA66:CH66" si="227">+CA37</f>
+        <f t="shared" ref="CA66:CH66" si="229">+CA37</f>
         <v>9680</v>
       </c>
       <c r="CB66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>11882</v>
       </c>
       <c r="CC66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>11724</v>
       </c>
       <c r="CD66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>11990</v>
       </c>
       <c r="CE66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>18262</v>
       </c>
       <c r="CF66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>21106</v>
       </c>
       <c r="CG66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>19902</v>
       </c>
       <c r="CH66" s="2">
-        <f t="shared" si="227"/>
+        <f t="shared" si="229"/>
         <v>19193</v>
       </c>
       <c r="CI66" s="2">
-        <f t="shared" ref="CI66:CJ66" si="228">+CI37</f>
+        <f t="shared" ref="CI66:CJ66" si="230">+CI37</f>
         <v>19765</v>
       </c>
       <c r="CJ66" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="230"/>
         <v>3751</v>
       </c>
     </row>
@@ -13028,83 +13060,83 @@
       <c r="W93" s="5"/>
       <c r="X93" s="5"/>
       <c r="BS93" s="6">
-        <f t="shared" ref="BS93:CE93" si="229">+BS77-BS79</f>
+        <f t="shared" ref="BS93:CE93" si="231">+BS77-BS79</f>
         <v>8980</v>
       </c>
       <c r="BT93" s="29">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>4772</v>
       </c>
       <c r="BU93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>7625</v>
       </c>
       <c r="BV93" s="29">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>5729</v>
       </c>
       <c r="BW93" s="29">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>6655</v>
       </c>
       <c r="BX93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>11485</v>
       </c>
       <c r="BY93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>15756</v>
       </c>
       <c r="BZ93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>7857</v>
       </c>
       <c r="CA93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>10065</v>
       </c>
       <c r="CB93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>10313</v>
       </c>
       <c r="CC93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>11691</v>
       </c>
       <c r="CD93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>12183</v>
       </c>
       <c r="CE93" s="6">
-        <f t="shared" si="229"/>
+        <f t="shared" si="231"/>
         <v>10332</v>
       </c>
       <c r="CF93" s="6">
-        <f t="shared" ref="CF93:CL93" si="230">+CF77+CF79</f>
+        <f t="shared" ref="CF93:CL93" si="232">+CF77+CF79</f>
         <v>14251</v>
       </c>
       <c r="CG93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>16932</v>
       </c>
       <c r="CH93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>21605</v>
       </c>
       <c r="CI93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>10723</v>
       </c>
       <c r="CJ93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>-9411</v>
       </c>
       <c r="CK93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>-14279</v>
       </c>
       <c r="CL93" s="6">
-        <f t="shared" si="230"/>
+        <f t="shared" si="232"/>
         <v>-12987</v>
       </c>
     </row>
@@ -13113,59 +13145,59 @@
         <v>145</v>
       </c>
       <c r="BY94" s="2">
-        <f t="shared" ref="BY94:CL94" si="231">+BY37-BY93</f>
+        <f t="shared" ref="BY94:CL94" si="233">+BY37-BY93</f>
         <v>-3050</v>
       </c>
       <c r="BZ94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>3127</v>
       </c>
       <c r="CA94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>-385</v>
       </c>
       <c r="CB94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>1569</v>
       </c>
       <c r="CC94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>33</v>
       </c>
       <c r="CD94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>-193</v>
       </c>
       <c r="CE94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>7930</v>
       </c>
       <c r="CF94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>6855</v>
       </c>
       <c r="CG94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>2970</v>
       </c>
       <c r="CH94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>-2412</v>
       </c>
       <c r="CI94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>9042</v>
       </c>
       <c r="CJ94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>13162</v>
       </c>
       <c r="CK94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>14811</v>
       </c>
       <c r="CL94" s="2">
-        <f t="shared" si="231"/>
+        <f t="shared" si="233"/>
         <v>8961.16</v>
       </c>
     </row>
@@ -13199,8 +13231,9 @@
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{5CF14BD8-3E10-4C93-8FB6-1B87FA509CB3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
